--- a/formats/xlsx/districts.xlsx
+++ b/formats/xlsx/districts.xlsx
@@ -13903,7 +13903,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Thung Khao Luangกิ่</t>
+          <t>Thung Khao Luang</t>
         </is>
       </c>
       <c r="D465" t="n">
